--- a/resources/zap/ZAP_JuiceShop.xlsx
+++ b/resources/zap/ZAP_JuiceShop.xlsx
@@ -486,23 +486,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SQL injection may be possible.</t>
+          <t>['SQL injection may be possible.']</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Do not trust client side input, even if there is client side validation in place.
-In general, type check all data on the server side.
-If the application uses JDBC, use PreparedStatement or CallableStatement, with parameters passed by '?'
-If the application uses ASP, use ADO Command Objects with strong type checking and parameterized queries.
-If database Stored Procedures can be used, use them.
-Do *not* concatenate strings into queries in the stored procedure, or use 'exec', 'exec immediate', or equivalent functionality!
-Do not create dynamic SQL queries using simple string concatenation.
-Escape all data received from the client.
-Apply an 'allow list' of allowed characters, or a 'deny list' of disallowed characters in user input.
-Apply the principle of least privilege by using the least privileged database user possible.
-In particular, avoid using the 'sa' or 'db-owner' database users. This does not eliminate SQL injection, but minimizes its impact.
-Grant the minimum database access that is necessary for the application.</t>
+          <t>['Do not trust client side input, even if there is client side validation in place.', 'In general, type check all data on the server side.', "If the application uses JDBC, use PreparedStatement or CallableStatement, with parameters passed by '?'", 'If the application uses ASP, use ADO Command Objects with strong type checking and parameterized queries.', 'If database Stored Procedures can be used, use them.', "Do *not* concatenate strings into queries in the stored procedure, or use 'exec', 'exec immediate', or equivalent functionality!", 'Do not create dynamic SQL queries using simple string concatenation.', 'Escape all data received from the client.', "Apply an 'allow list' of allowed characters, or a 'deny list' of disallowed characters in user input.", 'Apply the principle of least privilege by using the least privileged database user possible.', "In particular, avoid using the 'sa' or 'db-owner' database users. This does not eliminate SQL injection, but minimizes its impact.", 'Grant the minimum database access that is necessary for the application.']</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -541,12 +530,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Content Security Policy (CSP) is an added layer of security that helps to detect and mitigate certain types of attacks, including Cross Site Scripting (XSS) and data injection attacks. These attacks are used for everything from data theft to site defacement or distribution of malware. CSP provides a set of standard HTTP headers that allow website owners to declare approved sources of content that browsers should be allowed to load on that page — covered types are JavaScript, CSS, HTML frames, fonts, images and embeddable objects such as Java applets, ActiveX, audio and video files.</t>
+          <t>['Content Security Policy (CSP) is an added layer of security that helps to detect and mitigate certain types of attacks, including Cross Site Scripting (XSS) and data injection attacks. These attacks are used for everything from data theft to site defacement or distribution of malware. CSP provides a set of standard HTTP headers that allow website owners to declare approved sources of content that browsers should be allowed to load on that page — covered types are JavaScript, CSS, HTML frames, fonts, images and embeddable objects such as Java applets, ActiveX, audio and video files.']</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ensure that your web server, application server, load balancer, etc. is configured to set the Content-Security-Policy header.</t>
+          <t>['Ensure that your web server, application server, load balancer, etc. is configured to set the Content-Security-Policy header.']</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -585,13 +574,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Web browser data loading may be possible, due to a Cross Origin Resource Sharing (CORS) misconfiguration on the web server.</t>
+          <t>['Web browser data loading may be possible, due to a Cross Origin Resource Sharing (CORS) misconfiguration on the web server.']</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ensure that sensitive data is not available in an unauthenticated manner (using IP address white-listing, for instance).
-Configure the "Access-Control-Allow-Origin" HTTP header to a more restrictive set of domains, or remove all CORS headers entirely, to allow the web browser to enforce the Same Origin Policy (SOP) in a more restrictive manner.</t>
+          <t>['Ensure that sensitive data is not available in an unauthenticated manner (using IP address white-listing, for instance).', 'Configure the "Access-Control-Allow-Origin" HTTP header to a more restrictive set of domains, or remove all CORS headers entirely, to allow the web browser to enforce the Same Origin Policy (SOP) in a more restrictive manner.']</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -630,13 +618,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The response does not protect against 'ClickJacking' attacks. It should include either Content-Security-Policy with 'frame-ancestors' directive or X-Frame-Options.</t>
+          <t>["The response does not protect against 'ClickJacking' attacks. It should include either Content-Security-Policy with 'frame-ancestors' directive or X-Frame-Options."]</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Modern Web browsers support the Content-Security-Policy and X-Frame-Options HTTP headers. Ensure one of them is set on all web pages returned by your site/app.
-If you expect the page to be framed only by pages on your server (e.g. it's part of a FRAMESET) then you'll want to use SAMEORIGIN, otherwise if you never expect the page to be framed, you should use DENY. Alternatively consider implementing Content Security Policy's "frame-ancestors" directive.</t>
+          <t>['Modern Web browsers support the Content-Security-Policy and X-Frame-Options HTTP headers. Ensure one of them is set on all web pages returned by your site/app.', 'If you expect the page to be framed only by pages on your server (e.g. it\'s part of a FRAMESET) then you\'ll want to use SAMEORIGIN, otherwise if you never expect the page to be framed, you should use DENY. Alternatively consider implementing Content Security Policy\'s "frame-ancestors" directive.']</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -675,12 +662,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>URL rewrite is used to track user session ID. The session ID may be disclosed via cross-site referer header. In addition, the session ID might be stored in browser history or server logs.</t>
+          <t>['URL rewrite is used to track user session ID. The session ID may be disclosed via cross-site referer header. In addition, the session ID might be stored in browser history or server logs.']</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>For secure content, put session ID in a cookie. To be even more secure consider using a combination of cookie and URL rewrite.</t>
+          <t>['For secure content, put session ID in a cookie. To be even more secure consider using a combination of cookie and URL rewrite.']</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -719,12 +706,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A private IP (such as 10.x.x.x, 172.x.x.x, 192.168.x.x) or an Amazon EC2 private hostname (for example, ip-10-0-56-78) has been found in the HTTP response body. This information might be helpful for further attacks targeting internal systems.</t>
+          <t>['A private IP (such as 10.x.x.x, 172.x.x.x, 192.168.x.x) or an Amazon EC2 private hostname (for example, ip-10-0-56-78) has been found in the HTTP response body. This information might be helpful for further attacks targeting internal systems.']</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remove the private IP address from the HTTP response body. For comments, use JSP/ASP/PHP comment instead of HTML/JavaScript comment which can be seen by client browsers.</t>
+          <t>['Remove the private IP address from the HTTP response body. For comments, use JSP/ASP/PHP comment instead of HTML/JavaScript comment which can be seen by client browsers.']</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -763,12 +750,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A timestamp was disclosed by the application/web server. - Unix</t>
+          <t>['A timestamp was disclosed by the application/web server. - Unix']</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Manually confirm that the timestamp data is not sensitive, and that the data cannot be aggregated to disclose exploitable patterns.</t>
+          <t>['Manually confirm that the timestamp data is not sensitive, and that the data cannot be aggregated to disclose exploitable patterns.']</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -807,13 +794,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Anti-MIME-Sniffing header X-Content-Type-Options was not set to 'nosniff'. This allows older versions of Internet Explorer and Chrome to perform MIME-sniffing on the response body, potentially causing the response body to be interpreted and displayed as a content type other than the declared content type. Current (early 2014) and legacy versions of Firefox will use the declared content type (if one is set), rather than performing MIME-sniffing.</t>
+          <t>["The Anti-MIME-Sniffing header X-Content-Type-Options was not set to 'nosniff'. This allows older versions of Internet Explorer and Chrome to perform MIME-sniffing on the response body, potentially causing the response body to be interpreted and displayed as a content type other than the declared content type. Current (early 2014) and legacy versions of Firefox will use the declared content type (if one is set), rather than performing MIME-sniffing."]</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ensure that the application/web server sets the Content-Type header appropriately, and that it sets the X-Content-Type-Options header to 'nosniff' for all web pages.
-If possible, ensure that the end user uses a standards-compliant and modern web browser that does not perform MIME-sniffing at all, or that can be directed by the web application/web server to not perform MIME-sniffing.</t>
+          <t>["Ensure that the application/web server sets the Content-Type header appropriately, and that it sets the X-Content-Type-Options header to 'nosniff' for all web pages.", 'If possible, ensure that the end user uses a standards-compliant and modern web browser that does not perform MIME-sniffing at all, or that can be directed by the web application/web server to not perform MIME-sniffing.']</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -852,12 +838,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The application appears to be a modern web application. If you need to explore it automatically then the Ajax Spider may well be more effective than the standard one.</t>
+          <t>['The application appears to be a modern web application. If you need to explore it automatically then the Ajax Spider may well be more effective than the standard one.']</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>This is an informational alert and so no changes are required.</t>
+          <t>['This is an informational alert and so no changes are required.']</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -892,7 +878,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Check for differences in response based on fuzzed User Agent (eg. mobile sites, access as a Search Engine Crawler). Compares the response statuscode and the hashcode of the response body with the original response.</t>
+          <t>['Check for differences in response based on fuzzed User Agent (eg. mobile sites, access as a Search Engine Crawler). Compares the response statuscode and the hashcode of the response body with the original response.']</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
